--- a/outputs/meridian_april_2026_treasury_report.xlsx
+++ b/outputs/meridian_april_2026_treasury_report.xlsx
@@ -61,7 +61,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DRAFT / BLOCKED: do not submit until the 2026-04-28 stale cash row is refreshed.</t>
+          <t>DRAFT / BLOCKED: do not submit until the stale cash row(s) dated 2026-04-28 are refreshed.</t>
         </is>
       </c>
     </row>
@@ -401,7 +401,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DRAFT / BLOCKED: do not submit until the 2026-04-28 stale cash row is refreshed.</t>
+          <t>DRAFT / BLOCKED: do not submit until the stale cash row(s) dated 2026-04-28 are refreshed.</t>
         </is>
       </c>
     </row>
@@ -798,7 +798,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DRAFT / BLOCKED: do not submit until the 2026-04-28 stale cash row is refreshed.</t>
+          <t>DRAFT / BLOCKED: do not submit until the stale cash row(s) dated 2026-04-28 are refreshed.</t>
         </is>
       </c>
     </row>
@@ -1315,7 +1315,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DRAFT / BLOCKED: do not submit until the 2026-04-28 stale cash row is refreshed.</t>
+          <t>DRAFT / BLOCKED: do not submit until the stale cash row(s) dated 2026-04-28 are refreshed.</t>
         </is>
       </c>
     </row>
@@ -4460,7 +4460,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DRAFT / BLOCKED: do not submit until the 2026-04-28 stale cash row is refreshed.</t>
+          <t>DRAFT / BLOCKED: do not submit until the stale cash row(s) dated 2026-04-28 are refreshed.</t>
         </is>
       </c>
     </row>
@@ -4876,7 +4876,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DRAFT / BLOCKED: do not submit until the 2026-04-28 stale cash row is refreshed.</t>
+          <t>DRAFT / BLOCKED: do not submit until the stale cash row(s) dated 2026-04-28 are refreshed.</t>
         </is>
       </c>
     </row>
@@ -6856,7 +6856,7 @@
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>DRAFT / BLOCKED: do not submit until the 2026-04-28 stale cash row is refreshed.</t>
+          <t>DRAFT / BLOCKED: do not submit until the stale cash row(s) dated 2026-04-28 are refreshed.</t>
         </is>
       </c>
     </row>
@@ -6968,12 +6968,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>MF-004 EUR balances use incorrect USD conversion</t>
+          <t>MF-004 balances use incorrect USD conversion</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2 EUR row(s) are overstated by $252,000 versus the CFO-approved 1.08 EUR/USD rate.</t>
+          <t>2 EUR row(s) are overstated by $252,000 versus the CFO-approved rate(s) (1.08 EUR/USD).</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
